--- a/faq/cards.xlsx
+++ b/faq/cards.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
     <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -450,281 +450,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 'Проценты по счету карты «Прибыль» выплачиваются ежемесячно в дату открытия счета, на этот же счет. Начисление процентов происходит ежедневно на фактический остаток счета на начало дня.'</t>
+          <t xml:space="preserve">  - Моментальную карту можно получить в день обращения. Исключение – «Социальная карта Башкортостана» со сроком изготовления до 45 рабочих дней.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Проценты по счету карты «Прибыль» выплачиваются ежемесячно в дату открытия счета, на этот же счет. Начисление процентов происходит ежедневно на фактический остаток счета на начало дня.</t>
+          <t xml:space="preserve">  - Моментальную карту можно получить в день обращения. Исключение — «Социальная карта Башкортостана» со сроком изготовления до 45 рабочих дней.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>эн-дефис (–) заменён на тире (—)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 'Для начисления процентов в текущем месяце нужно совершить покупки по карте на сумму от 10 000 рублей в предыдущем месяце.'</t>
+          <t xml:space="preserve">  'Выплата процентов осуществляется ежемесячно в дату открытия счета карты путем капитализации – причисления суммы процентов на счет.'</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Для начисления процентов в текущем месяце нужно совершить покупки по карте на сумму от 10 000 рублей в предыдущем месяце.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 'При невыполнении условий бесплатности за обслуживание карты комиссия списывается 5 числа месяца.'</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>При невыполнении условий бесплатности за обслуживание карты комиссия списывается 5 числа месяца.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 'Если 5 число выпадает на нерабочий или праздничный день, дата списания переносится на ближайший рабочий день.'</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Если 5 число выпадает на нерабочий или праздничный день, дата списания переносится на ближайший рабочий день.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Для выполнения условий бесплатности учитываются траты по карте, совершенные в текущем месяце.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Для выполнения условий бесплатности учитываются траты по карте, совершенные в текущем месяце.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Исключения составляют операции с MCC, указанные в тарифном плане.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Исключения составляют операции с MCC, указанные в тарифном плане.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Выпуск новых карт Priority Pass прекращен с 25.07.2022 г. В том числе остановлен и перевыпуск карт Priority Pass по любой из причин, и все ранее выпущенные карты Priority Pass будут закрыты.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Выпуск новых карт Priority Pass прекращен с 25.07.2022 г. В том числе остановлен и перевыпуск карт Priority Pass по любой из причин, и все ранее выпущенные карты Priority Pass будут закрыты.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>12</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - В качестве альтернативы владельцам премиальных пакетов услуг при наличии активной карты Mir Supreme сейчас доступен сервис Mir Pass.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>В качестве альтернативы владельцам премиальных пакетов услуг при наличии активной карты Mir Supreme сейчас доступен сервис Mir Pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 'Комиссия за обслуживание пакета услуг за текущий месяц будет списана в следующем месяце.'</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Комиссия за обслуживание пакета услуг за текущий месяц будет списана в следующем месяце.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>15</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 'Комиссия за обслуживание не списывается первые 2 месяца. Календарный месяц, в котором был приобретен пакет и следующий за ним. Со второго месяца необходимо выполнять условия бесплатности.'</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Комиссия за обслуживание не списывается первые 2 месяца. Календарный месяц, в котором был приобретен пакет и следующий за ним. Со второго месяца необходимо выполнять условия бесплатности.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>17</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Именная карта изготавливается до 14 рабочих дней.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Именная карта изготавливается до 14 рабочих дней.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>19</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Моментальную карту можно получить в день обращения.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Моментальную карту можно получить в день обращения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>22</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Именная карта изготавливается до 10 рабочих дней.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Именная карта изготавливается до 10 рабочих дней.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>23</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Моментальную карту можно получить в день обращения. Исключение – «Социальная карта Башкортостана» со сроком изготовления до 45 рабочих дней.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Моментальную карту можно получить в день обращения. Исключение — «Социальная карта Башкортостана» со сроком изготовления до 45 рабочих дней.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t xml:space="preserve">  'Выплата процентов осуществляется ежемесячно в дату открытия счета карты путем капитализации — причисления суммы процентов на счет.'</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>эн-дефис (–) заменён на тире (—)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>26</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  'Выплата процентов осуществляется ежемесячно в дату открытия счета карты путем капитализации – причисления суммы процентов на счет.'</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Выплата процентов осуществляется ежемесячно в дату открытия счета карты путем капитализации — причисления суммы процентов на счет.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>эн-дефис (–) заменён на тире (—)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>29</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 'На главном экране «Уралсиб Онлайн» выберите кредитную карту. Вам откроется информация о доступном балансе, сумме задолженности. Там же вы увидите сумму и дату погашения ближайшего минимального ежемесячного платежа.'</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>На главном экране «Уралсиб Онлайн» выберите кредитную карту. Вам откроется информация о доступном балансе, сумме задолженности. Там же вы увидите сумму и дату погашения ближайшего минимального ежемесячного платежа.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>31</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Расчет минимального платежа: 3% от суммы задолженности плюс начисленные проценты за предыдущий период.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Расчет минимального платежа: 3% от суммы задолженности плюс начисленные проценты за предыдущий период.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>33</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Сумма минимального платежа составит не менее 300 рублей.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Сумма минимального платежа составит не менее 300 рублей.</t>
         </is>
       </c>
     </row>
